--- a/artfynd/A 63201-2025 artfynd.xlsx
+++ b/artfynd/A 63201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,2411 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130937843</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>489760</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7004232</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd längs flera meter högt upp på en granstam med spår av rikligt sav/kådaflöde.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130937857</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97845</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489680</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7004154</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130937854</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>489668</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7004128</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår, färska och äldre, I två levande granar och i ytlig grov rotdel.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130937863</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98974</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489799</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7004245</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor inom ca 1 m2 yta. Grävdes varsamt fram under snötäcket. Det finns sannolikt betydligt mer knärot på fyndplatsen och i skogsbeståndet där fyndplatsen ligger.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130937852</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>489520</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7004161</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, ytliga enstaka längs flera meter på en granstam vid kanten mot yngre skog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130937848</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489561</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7004194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, enstaka på en yngre mer slät granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130937845</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489591</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7004200</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, enstaka längs några meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130937849</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>489552</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7004190</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130937856</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97845</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>489713</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7004214</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer här i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130937862</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99308</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489672</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7004126</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 vissen stjälk med bär. I granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130937850</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>489555</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7004193</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Tydliga spår av sav/kådaflöde på granstammen. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130937847</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>489574</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7004196</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, enstaka långt upp på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130937851</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>489543</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7004184</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, ett par enstaka på ca 1,9 meters höjd på en granstam vid kant mot yngre skog.  Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130937844</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>489610</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7004216</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130937859</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97845</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>489676</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7004169</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130937853</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>489526</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7004167</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, enstaka några meter upp på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130937860</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97845</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>489614</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7004216</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Växer här i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130937846</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>489591</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7004206</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, främst färska och några äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog intill några rotvältor.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130937858</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97845</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>489700</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7004142</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63201-2025 artfynd.xlsx
+++ b/artfynd/A 63201-2025 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130937843</v>
+        <v>130937854</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489760</v>
+        <v>489668</v>
       </c>
       <c r="R3" t="n">
-        <v>7004232</v>
+        <v>7004128</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, i riklig mängd längs flera meter högt upp på en granstam med spår av rikligt sav/kådaflöde.</t>
+          <t>Rejäla hackspår, färska och äldre, I två levande granar och i ytlig grov rotdel.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,38 +941,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130937857</v>
+        <v>130937843</v>
       </c>
       <c r="B4" t="n">
-        <v>97845</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489680</v>
+        <v>489760</v>
       </c>
       <c r="R4" t="n">
-        <v>7004154</v>
+        <v>7004232</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,19 +1022,43 @@
           <t>2026-01-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd längs flera meter högt upp på en granstam med spår av rikligt sav/kådaflöde.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130937854</v>
+        <v>130937852</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,16 +1087,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1081,7 +1109,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1091,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489668</v>
+        <v>489520</v>
       </c>
       <c r="R5" t="n">
-        <v>7004128</v>
+        <v>7004161</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1159,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår, färska och äldre, I två levande granar och i ytlig grov rotdel.</t>
+          <t>Ringhack, äldre, ytliga enstaka längs flera meter på en granstam vid kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,49 +1211,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130937863</v>
+        <v>130937857</v>
       </c>
       <c r="B6" t="n">
-        <v>98974</v>
+        <v>97854</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1234,10 +1250,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489799</v>
+        <v>489680</v>
       </c>
       <c r="R6" t="n">
-        <v>7004245</v>
+        <v>7004154</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,11 +1288,6 @@
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor inom ca 1 m2 yta. Grävdes varsamt fram under snötäcket. Det finns sannolikt betydligt mer knärot på fyndplatsen och i skogsbeståndet där fyndplatsen ligger.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1289,7 +1300,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1307,42 +1318,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130937852</v>
+        <v>130937863</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>98988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1350,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489520</v>
+        <v>489799</v>
       </c>
       <c r="R7" t="n">
-        <v>7004161</v>
+        <v>7004245</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1390,7 +1409,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, ytliga enstaka längs flera meter på en granstam vid kanten mot yngre skog.</t>
+          <t>Minst 8 plantor inom ca 1 m2 yta. Grävdes varsamt fram under snötäcket. Det finns sannolikt betydligt mer knärot på fyndplatsen och i skogsbeståndet där fyndplatsen ligger.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,32 +1418,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1850,7 +1850,7 @@
         <v>130937856</v>
       </c>
       <c r="B11" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>130937862</v>
       </c>
       <c r="B12" t="n">
-        <v>99308</v>
+        <v>99322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>130937859</v>
       </c>
       <c r="B17" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>130937860</v>
       </c>
       <c r="B19" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>130937858</v>
       </c>
       <c r="B21" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 63201-2025 artfynd.xlsx
+++ b/artfynd/A 63201-2025 artfynd.xlsx
@@ -1321,7 +1321,7 @@
         <v>130937863</v>
       </c>
       <c r="B7" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1712,42 +1712,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130937849</v>
+        <v>130937856</v>
       </c>
       <c r="B10" t="n">
-        <v>57864</v>
+        <v>97854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1755,10 +1751,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489552</v>
+        <v>489713</v>
       </c>
       <c r="R10" t="n">
-        <v>7004190</v>
+        <v>7004214</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,7 +1791,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+          <t>Växer här i barrblandskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1804,32 +1800,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1847,38 +1824,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130937856</v>
+        <v>130937849</v>
       </c>
       <c r="B11" t="n">
-        <v>97854</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1886,10 +1867,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489713</v>
+        <v>489552</v>
       </c>
       <c r="R11" t="n">
-        <v>7004214</v>
+        <v>7004190</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1926,7 +1907,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växer här i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,13 +1916,32 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
         <v>130937862</v>
       </c>
       <c r="B12" t="n">
-        <v>99322</v>
+        <v>99326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 63201-2025 artfynd.xlsx
+++ b/artfynd/A 63201-2025 artfynd.xlsx
@@ -3214,7 +3214,7 @@
         <v>134180643</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>134180646</v>
       </c>
       <c r="B23" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>134180636</v>
       </c>
       <c r="B24" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>134180634</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>134180642</v>
       </c>
       <c r="B26" t="n">
-        <v>99205</v>
+        <v>99212</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>134180632</v>
       </c>
       <c r="B27" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>134180638</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>134180647</v>
       </c>
       <c r="B30" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>134180631</v>
       </c>
       <c r="B31" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134180630</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>134180641</v>
       </c>
       <c r="B33" t="n">
-        <v>99205</v>
+        <v>99212</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>134180639</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>134180633</v>
       </c>
       <c r="B35" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 63201-2025 artfynd.xlsx
+++ b/artfynd/A 63201-2025 artfynd.xlsx
@@ -675,62 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129222155</v>
+        <v>134180645</v>
       </c>
       <c r="B2" t="n">
-        <v>57834</v>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storflon, Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489559</v>
+        <v>489844</v>
       </c>
       <c r="R2" t="n">
-        <v>7004186</v>
+        <v>7004448</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +743,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Synobservation av en lavskrika som uttryckte lockläte i en grantopp.</t>
+          <t>På gammal sälg, rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,33 +772,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130937843</v>
+        <v>134180647</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>80489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,45 +802,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489760</v>
+        <v>489821</v>
       </c>
       <c r="R3" t="n">
-        <v>7004232</v>
+        <v>7004389</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,17 +859,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, i riklig mängd längs flera meter högt upp på en granstam med spår av rikligt sav/kådaflöde.</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,99 +888,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130937852</v>
+        <v>134180630</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489520</v>
+        <v>489845</v>
       </c>
       <c r="R4" t="n">
-        <v>7004161</v>
+        <v>7004452</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,17 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, ytliga enstaka längs flera meter på en granstam vid kanten mot yngre skog.</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,97 +998,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130937854</v>
+        <v>134180634</v>
       </c>
       <c r="B5" t="n">
-        <v>57881</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489668</v>
+        <v>489855</v>
       </c>
       <c r="R5" t="n">
-        <v>7004128</v>
+        <v>7004394</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1149,17 +1079,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår, färska och äldre, I två levande granar och i ytlig grov rotdel.</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,51 +1105,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130937863</v>
+        <v>134180638</v>
       </c>
       <c r="B6" t="n">
-        <v>99015</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,53 +1132,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489799</v>
+        <v>489870</v>
       </c>
       <c r="R6" t="n">
-        <v>7004245</v>
+        <v>7004317</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,17 +1186,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor inom ca 1 m2 yta. Grävdes varsamt fram under snötäcket. Det finns sannolikt betydligt mer knärot på fyndplatsen och i skogsbeståndet där fyndplatsen ligger.</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,76 +1210,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130937857</v>
+        <v>134180639</v>
       </c>
       <c r="B7" t="n">
-        <v>97880</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489680</v>
+        <v>489821</v>
       </c>
       <c r="R7" t="n">
-        <v>7004154</v>
+        <v>7004389</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1404,12 +1293,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1418,80 +1317,69 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130937848</v>
+        <v>134180643</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489561</v>
+        <v>489844</v>
       </c>
       <c r="R8" t="n">
-        <v>7004194</v>
+        <v>7004448</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1515,17 +1403,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, enstaka på en yngre mer slät granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1534,53 +1427,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130937845</v>
+        <v>134180631</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,45 +1457,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489591</v>
+        <v>489844</v>
       </c>
       <c r="R9" t="n">
-        <v>7004200</v>
+        <v>7004448</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,17 +1511,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, enstaka längs några meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,51 +1542,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130937849</v>
+        <v>134180633</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,45 +1569,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489552</v>
+        <v>489843</v>
       </c>
       <c r="R10" t="n">
-        <v>7004190</v>
+        <v>7004404</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1785,17 +1623,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+          <t>På gammal döende rönn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,93 +1654,64 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130937856</v>
+        <v>134180636</v>
       </c>
       <c r="B11" t="n">
-        <v>97880</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489713</v>
+        <v>489859</v>
       </c>
       <c r="R11" t="n">
-        <v>7004214</v>
+        <v>7004398</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1916,17 +1735,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Växer här i barrblandskog.</t>
+          <t>På låga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,34 +1764,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130937862</v>
+        <v>134180632</v>
       </c>
       <c r="B12" t="n">
-        <v>99352</v>
+        <v>80493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1970,45 +1793,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219880</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489672</v>
+        <v>489842</v>
       </c>
       <c r="R12" t="n">
-        <v>7004126</v>
+        <v>7004440</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2032,17 +1847,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 vissen stjälk med bär. I granskog med stor stamdiameterspridning.</t>
+          <t>På levande asp och intilliggande björk låga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,51 +1876,45 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130937850</v>
+        <v>130937854</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2118,10 +1937,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489555</v>
+        <v>489668</v>
       </c>
       <c r="R13" t="n">
-        <v>7004193</v>
+        <v>7004128</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2158,7 +1977,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Tydliga spår av sav/kådaflöde på granstammen. Fyndplatsen finns i barrblandskog.</t>
+          <t>Rejäla hackspår, färska och äldre, I två levande granar och i ytlig grov rotdel.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2172,7 +1991,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2210,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130937847</v>
+        <v>130937843</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2253,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489574</v>
+        <v>489760</v>
       </c>
       <c r="R14" t="n">
-        <v>7004196</v>
+        <v>7004232</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2293,7 +2112,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka långt upp på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+          <t>Ringhack, färska och äldre, i riklig mängd längs flera meter högt upp på en granstam med spår av rikligt sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2307,7 +2126,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2345,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130937851</v>
+        <v>130937844</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2378,7 +2197,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2388,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>489543</v>
+        <v>489610</v>
       </c>
       <c r="R15" t="n">
-        <v>7004184</v>
+        <v>7004216</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2428,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, ett par enstaka på ca 1,9 meters höjd på en granstam vid kant mot yngre skog.  Fyndplatsen finns i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2480,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130937844</v>
+        <v>130937845</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2523,10 +2342,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489610</v>
+        <v>489591</v>
       </c>
       <c r="R16" t="n">
-        <v>7004216</v>
+        <v>7004200</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2563,7 +2382,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, enstaka längs några meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2615,38 +2434,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130937859</v>
+        <v>130937846</v>
       </c>
       <c r="B17" t="n">
-        <v>97880</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2654,10 +2477,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489676</v>
+        <v>489591</v>
       </c>
       <c r="R17" t="n">
-        <v>7004169</v>
+        <v>7004206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2692,19 +2515,43 @@
           <t>2026-01-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, främst färska och några äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog intill några rotvältor.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2722,10 +2569,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130937853</v>
+        <v>130937847</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2765,10 +2612,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>489526</v>
+        <v>489574</v>
       </c>
       <c r="R18" t="n">
-        <v>7004167</v>
+        <v>7004196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2805,7 +2652,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, enstaka några meter upp på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
+          <t>Ringhack (savhack), färska, enstaka långt upp på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2857,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130937846</v>
+        <v>130937848</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2900,10 +2747,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>489591</v>
+        <v>489561</v>
       </c>
       <c r="R19" t="n">
-        <v>7004206</v>
+        <v>7004194</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2940,7 +2787,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, främst färska och några äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog intill några rotvältor.</t>
+          <t>Ringhack (savhack), färska och äldre, enstaka på en yngre mer slät granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2992,38 +2839,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130937860</v>
+        <v>130937849</v>
       </c>
       <c r="B20" t="n">
-        <v>97880</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3031,10 +2882,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>489614</v>
+        <v>489552</v>
       </c>
       <c r="R20" t="n">
-        <v>7004216</v>
+        <v>7004190</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3071,7 +2922,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Växer här i barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3080,13 +2931,32 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3104,38 +2974,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130937858</v>
+        <v>130937850</v>
       </c>
       <c r="B21" t="n">
-        <v>97880</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3143,10 +3017,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>489700</v>
+        <v>489555</v>
       </c>
       <c r="R21" t="n">
-        <v>7004142</v>
+        <v>7004193</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3181,19 +3055,43 @@
           <t>2026-01-28</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam vid kant mot yngre skog. Tydliga spår av sav/kådaflöde på granstammen. Fyndplatsen finns i barrblandskog.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3211,10 +3109,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134180643</v>
+        <v>130937851</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3222,40 +3120,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>489844</v>
+        <v>489543</v>
       </c>
       <c r="R22" t="n">
-        <v>7004448</v>
+        <v>7004184</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3279,22 +3182,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, ett par enstaka på ca 1,9 meters höjd på en granstam vid kant mot yngre skog.  Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3303,29 +3201,53 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134180646</v>
+        <v>130937852</v>
       </c>
       <c r="B23" t="n">
-        <v>80482</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3333,40 +3255,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>489844</v>
+        <v>489520</v>
       </c>
       <c r="R23" t="n">
-        <v>7004448</v>
+        <v>7004161</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3390,27 +3317,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal sälg. Mkt rikligt med suraler</t>
+          <t>Ringhack, äldre, ytliga enstaka längs flera meter på en granstam vid kanten mot yngre skog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,29 +3336,53 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134180636</v>
+        <v>130937853</v>
       </c>
       <c r="B24" t="n">
-        <v>80481</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3449,37 +3390,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>489859</v>
+        <v>489526</v>
       </c>
       <c r="R24" t="n">
-        <v>7004398</v>
+        <v>7004167</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3503,27 +3452,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På låga</t>
+          <t>Ringhack (savhack), färska, enstaka några meter upp på en granstam vid kant mot yngre skog. Fyndplatsen finns i barrblandskog.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3534,48 +3473,73 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134180634</v>
+        <v>134180637</v>
       </c>
       <c r="B25" t="n">
-        <v>79366</v>
+        <v>57153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3585,13 +3549,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>489855</v>
+        <v>489856</v>
       </c>
       <c r="R25" t="n">
-        <v>7004394</v>
+        <v>7004393</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3620,7 +3584,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3630,7 +3594,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3657,56 +3621,62 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134180642</v>
+        <v>129222155</v>
       </c>
       <c r="B26" t="n">
-        <v>99212</v>
+        <v>58057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>489844</v>
+        <v>489559</v>
       </c>
       <c r="R26" t="n">
-        <v>7004448</v>
+        <v>7004186</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3730,22 +3700,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Synobservation av en lavskrika som uttryckte lockläte i en grantopp.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3754,29 +3729,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134180632</v>
+        <v>134180641</v>
       </c>
       <c r="B27" t="n">
-        <v>80486</v>
+        <v>99219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3784,34 +3763,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>489842</v>
+        <v>489820</v>
       </c>
       <c r="R27" t="n">
-        <v>7004440</v>
+        <v>7004359</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3843,7 +3826,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3853,12 +3836,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På levande asp och intilliggande björk låga.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3885,48 +3863,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134180637</v>
+        <v>134180642</v>
       </c>
       <c r="B28" t="n">
-        <v>57153</v>
+        <v>99219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>489856</v>
+        <v>489844</v>
       </c>
       <c r="R28" t="n">
-        <v>7004393</v>
+        <v>7004448</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3955,7 +3941,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3965,7 +3951,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3974,6 +3960,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3992,48 +3979,56 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134180638</v>
+        <v>130937862</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>99456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>489870</v>
+        <v>489672</v>
       </c>
       <c r="R29" t="n">
-        <v>7004317</v>
+        <v>7004126</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4057,22 +4052,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 vissen stjälk med bär. I granskog med stor stamdiameterspridning.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4081,69 +4071,88 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134180647</v>
+        <v>130937863</v>
       </c>
       <c r="B30" t="n">
-        <v>80482</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>489821</v>
+        <v>489799</v>
       </c>
       <c r="R30" t="n">
-        <v>7004389</v>
+        <v>7004245</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4167,27 +4176,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:09</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Minst 8 plantor inom ca 1 m2 yta. Grävdes varsamt fram under snötäcket. Det finns sannolikt betydligt mer knärot på fyndplatsen och i skogsbeståndet där fyndplatsen ligger.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4200,63 +4199,72 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134180631</v>
+        <v>130937856</v>
       </c>
       <c r="B31" t="n">
-        <v>80481</v>
+        <v>97983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>489844</v>
+        <v>489713</v>
       </c>
       <c r="R31" t="n">
-        <v>7004448</v>
+        <v>7004214</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4280,27 +4288,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Växer här i barrblandskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4309,66 +4307,76 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134180630</v>
+        <v>130937857</v>
       </c>
       <c r="B32" t="n">
-        <v>79366</v>
+        <v>97983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>489845</v>
+        <v>489680</v>
       </c>
       <c r="R32" t="n">
-        <v>7004452</v>
+        <v>7004154</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4392,22 +4400,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4416,28 +4414,34 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134180641</v>
+        <v>130937858</v>
       </c>
       <c r="B33" t="n">
-        <v>99212</v>
+        <v>97983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4445,41 +4449,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>489820</v>
+        <v>489700</v>
       </c>
       <c r="R33" t="n">
-        <v>7004359</v>
+        <v>7004142</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4503,22 +4507,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4527,66 +4521,76 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134180639</v>
+        <v>130937859</v>
       </c>
       <c r="B34" t="n">
-        <v>79366</v>
+        <v>97983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>489821</v>
+        <v>489676</v>
       </c>
       <c r="R34" t="n">
-        <v>7004389</v>
+        <v>7004169</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4610,22 +4614,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4634,66 +4628,76 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134180633</v>
+        <v>130937860</v>
       </c>
       <c r="B35" t="n">
-        <v>80481</v>
+        <v>97983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storsved, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>489843</v>
+        <v>489614</v>
       </c>
       <c r="R35" t="n">
-        <v>7004404</v>
+        <v>7004216</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4717,27 +4721,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal döende rönn</t>
+          <t>Växer här i barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4746,18 +4740,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 63201-2025 artfynd.xlsx
+++ b/artfynd/A 63201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180647</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180630</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180634</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180638</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180643</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180631</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180633</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1779,6 +1829,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180636</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180632</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937854</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937843</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2296,6 +2366,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937844</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2431,6 +2506,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937845</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2566,6 +2646,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937846</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2701,6 +2786,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937847</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2836,6 +2926,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937848</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2971,6 +3066,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937849</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3106,6 +3206,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937850</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3241,6 +3346,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937851</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3376,6 +3486,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937852</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3511,6 +3626,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937853</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3618,6 +3738,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180637</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3749,6 +3874,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129222155</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3860,6 +3990,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180641</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3976,6 +4111,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180642</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4092,6 +4232,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937862</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4216,6 +4361,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937863</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4328,6 +4478,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937856</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4435,6 +4590,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937857</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4542,6 +4702,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937858</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4649,6 +4814,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937859</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4761,8 +4931,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130937860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>